--- a/artfynd/A 1201-2025 artfynd.xlsx
+++ b/artfynd/A 1201-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122585311</v>
+        <v>122585309</v>
       </c>
       <c r="B2" t="n">
         <v>98237</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>539549</v>
+        <v>539649</v>
       </c>
       <c r="R2" t="n">
-        <v>6403269</v>
+        <v>6403217</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122585309</v>
+        <v>122585316</v>
       </c>
       <c r="B3" t="n">
         <v>98237</v>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>539649</v>
+        <v>539557</v>
       </c>
       <c r="R3" t="n">
-        <v>6403217</v>
+        <v>6403247</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,7 +905,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122585316</v>
+        <v>122585311</v>
       </c>
       <c r="B4" t="n">
         <v>98237</v>
@@ -940,7 +940,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539557</v>
+        <v>539549</v>
       </c>
       <c r="R4" t="n">
-        <v>6403247</v>
+        <v>6403269</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 1201-2025 artfynd.xlsx
+++ b/artfynd/A 1201-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122585309</v>
       </c>
       <c r="B2" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122585316</v>
+        <v>122585311</v>
       </c>
       <c r="B3" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>539557</v>
+        <v>539549</v>
       </c>
       <c r="R3" t="n">
-        <v>6403247</v>
+        <v>6403269</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122585311</v>
+        <v>122585316</v>
       </c>
       <c r="B4" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539549</v>
+        <v>539557</v>
       </c>
       <c r="R4" t="n">
-        <v>6403269</v>
+        <v>6403247</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 1201-2025 artfynd.xlsx
+++ b/artfynd/A 1201-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122585309</v>
+        <v>122585316</v>
       </c>
       <c r="B2" t="n">
         <v>98240</v>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>539649</v>
+        <v>539557</v>
       </c>
       <c r="R2" t="n">
-        <v>6403217</v>
+        <v>6403247</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122585311</v>
+        <v>122585309</v>
       </c>
       <c r="B3" t="n">
         <v>98240</v>
@@ -825,7 +825,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>539549</v>
+        <v>539649</v>
       </c>
       <c r="R3" t="n">
-        <v>6403269</v>
+        <v>6403217</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,7 +905,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122585316</v>
+        <v>122585311</v>
       </c>
       <c r="B4" t="n">
         <v>98240</v>
@@ -940,7 +940,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539557</v>
+        <v>539549</v>
       </c>
       <c r="R4" t="n">
-        <v>6403247</v>
+        <v>6403269</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 1201-2025 artfynd.xlsx
+++ b/artfynd/A 1201-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122585316</v>
+        <v>122585311</v>
       </c>
       <c r="B2" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>539557</v>
+        <v>539549</v>
       </c>
       <c r="R2" t="n">
-        <v>6403247</v>
+        <v>6403269</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -793,7 +793,7 @@
         <v>122585309</v>
       </c>
       <c r="B3" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122585311</v>
+        <v>122585316</v>
       </c>
       <c r="B4" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539549</v>
+        <v>539557</v>
       </c>
       <c r="R4" t="n">
-        <v>6403269</v>
+        <v>6403247</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 1201-2025 artfynd.xlsx
+++ b/artfynd/A 1201-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122585311</v>
+        <v>122585316</v>
       </c>
       <c r="B2" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>539549</v>
+        <v>539557</v>
       </c>
       <c r="R2" t="n">
-        <v>6403269</v>
+        <v>6403247</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -793,7 +793,7 @@
         <v>122585309</v>
       </c>
       <c r="B3" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122585316</v>
+        <v>122585311</v>
       </c>
       <c r="B4" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539557</v>
+        <v>539549</v>
       </c>
       <c r="R4" t="n">
-        <v>6403247</v>
+        <v>6403269</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 1201-2025 artfynd.xlsx
+++ b/artfynd/A 1201-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122585316</v>
+        <v>122585311</v>
       </c>
       <c r="B2" t="n">
         <v>98244</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>539557</v>
+        <v>539549</v>
       </c>
       <c r="R2" t="n">
-        <v>6403247</v>
+        <v>6403269</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122585309</v>
+        <v>122585316</v>
       </c>
       <c r="B3" t="n">
         <v>98244</v>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>539649</v>
+        <v>539557</v>
       </c>
       <c r="R3" t="n">
-        <v>6403217</v>
+        <v>6403247</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,7 +905,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122585311</v>
+        <v>122585309</v>
       </c>
       <c r="B4" t="n">
         <v>98244</v>
@@ -940,7 +940,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539549</v>
+        <v>539649</v>
       </c>
       <c r="R4" t="n">
-        <v>6403269</v>
+        <v>6403217</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 1201-2025 artfynd.xlsx
+++ b/artfynd/A 1201-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122585311</v>
+        <v>122585316</v>
       </c>
       <c r="B2" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>539549</v>
+        <v>539557</v>
       </c>
       <c r="R2" t="n">
-        <v>6403269</v>
+        <v>6403247</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -793,7 +793,7 @@
         <v>122585309</v>
       </c>
       <c r="B3" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122585316</v>
+        <v>122585311</v>
       </c>
       <c r="B4" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539557</v>
+        <v>539549</v>
       </c>
       <c r="R4" t="n">
-        <v>6403247</v>
+        <v>6403269</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 1201-2025 artfynd.xlsx
+++ b/artfynd/A 1201-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122585316</v>
+        <v>122585311</v>
       </c>
       <c r="B2" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>539557</v>
+        <v>539549</v>
       </c>
       <c r="R2" t="n">
-        <v>6403247</v>
+        <v>6403269</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -793,7 +793,7 @@
         <v>122585309</v>
       </c>
       <c r="B3" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122585311</v>
+        <v>122585316</v>
       </c>
       <c r="B4" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539549</v>
+        <v>539557</v>
       </c>
       <c r="R4" t="n">
-        <v>6403269</v>
+        <v>6403247</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 1201-2025 artfynd.xlsx
+++ b/artfynd/A 1201-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122585311</v>
+        <v>122585316</v>
       </c>
       <c r="B2" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>539549</v>
+        <v>539557</v>
       </c>
       <c r="R2" t="n">
-        <v>6403269</v>
+        <v>6403247</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -793,7 +793,7 @@
         <v>122585309</v>
       </c>
       <c r="B3" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122585316</v>
+        <v>122585311</v>
       </c>
       <c r="B4" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539557</v>
+        <v>539549</v>
       </c>
       <c r="R4" t="n">
-        <v>6403247</v>
+        <v>6403269</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 1201-2025 artfynd.xlsx
+++ b/artfynd/A 1201-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122585316</v>
+        <v>122585277</v>
       </c>
       <c r="B2" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>539557</v>
+        <v>539658</v>
       </c>
       <c r="R2" t="n">
-        <v>6403247</v>
+        <v>6403240</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -793,12 +788,7 @@
         <v>122585309</v>
       </c>
       <c r="B3" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,12 +898,7 @@
         <v>122585311</v>
       </c>
       <c r="B4" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,6 +1002,116 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122585316</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lindefall, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>539557</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6403247</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Södra Vi</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1201-2025 artfynd.xlsx
+++ b/artfynd/A 1201-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122585277</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122585309</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122585311</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,8 +1132,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122585316</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>